--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0054.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0054.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Ác mộng của kẻ tan vỡ</t>
+          <t>Ác Mộng Vỡ Tan</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Glowing Thundering Mephis</t>
+          <t>Mephis Sấm Chớp Rực Rỡ</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Exile Technician</t>
+          <t>Kỹ Sư Lưu Đày</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Control Panel</t>
+          <t>Bảng Điều Khiển</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bắt đầu bài kiểm tra</t>
+          <t>Bắt Đầu Kiểm Tra</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Kiểm tra các mục tiêu bắt buộc</t>
+          <t>Kiểm tra số lượng yêu cầu đã bắt được</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Bouquet</t>
+          <t>Bó Hoa</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Gedao</t>
+          <t>Cách Đảo</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Platform Guardian</t>
+          <t>Người Bảo Vệ Nền Tảng</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Echo Challenge: Gulpuff</t>
+          <t>Thử Thách Tiếng Vọng: Gulpuff</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>False Sovereign</t>
+          <t>Chúa tể giả hiệu</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Guanghui</t>
+          <t>Quang Huy</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Signor Octopus</t>
+          <t>Ngài Bạch Tuộc</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Hovering Magnetite</t>
+          <t>Magnetit Bay Lượn</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Cantarella Cube</t>
+          <t>Khối Cantarella</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Nhân viên nghiêm túc</t>
+          <t>Nhân Viên Nghiêm Túc</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Plush Dream</t>
+          <t>Giấc Mơ Nhung Lụa</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Light Builder</t>
+          <t>Thợ Xây Ánh Sáng</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Voidspawn: Geospider S4</t>
+          <t>Voidspawn: Nhện Địa S4</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Into the dream with Metaphors</t>
+          <t>Đắm chìm vào giấc mơ với Ẩn Dụ</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Huanliu</t>
+          <t>Hoàn Lưu</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Explosive Barrel</t>
+          <t>Thùng nổ</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Stained glass on the right</t>
+          <t>Mảnh Kính Màu Bên Phải</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Kronablight</t>
+          <t>Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Irritated Staff</t>
+          <t>Nhân Viên Bực Tức</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Music Stand</t>
+          <t>Giá Đỡ Bản Nhạc</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Injured Researcher</t>
+          <t>Nhà Nghiên Cứu Bị Thương</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Havoc Drake</t>
+          <t>Drake Hỗn Loạn</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Peep</t>
+          <t>Peep là một Soliskin. Đối tượng nghiên cứu của chúng ta.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Đến Dimmr Plains</t>
+          <t>Đến Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Play Lahai-Roi Blocks</t>
+          <t>Chơi Nhịp Điệu Lahai-Roi</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Pioneer Association Commissions</t>
+          <t>Nhiệm Vụ của Hiệp Hội Tiên Phong</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Turn On</t>
+          <t>Bật</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Large Fishing Spot</t>
+          <t>Bãi câu cá lớn</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Enter Sonoro Sphere</t>
+          <t>Vào Sonoro Sphere</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Qianshan</t>
+          <t>Kiền Sơn</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Ảo tưởng không trở lại</t>
+          <t>Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Cradle Lichen</t>
+          <t>Địa Y Nôi Trú</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Điều tra màn hình</t>
+          <t>Kiểm tra màn hình</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Strange Rabbit</t>
+          <t>Thỏ Kỳ Lạ</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Chase</t>
+          <t>Truy đuổi</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Firecracker Jewelweed</t>
+          <t>Cỏ Lửa Đom Đóm</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Golden Junrock</t>
+          <t>Junrock Vàng</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Frostcrest Gladiator</t>
+          <t>Đấu Sĩ Sương Tuyết</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Sea Apple</t>
+          <t>Táo Biển</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Capsule Machine</t>
+          <t>Máy Nén Viên Nang</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Retriever</t>
+          <t>Người Thu Thập</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Doll Vendor Invidia</t>
+          <t>Người Bán Búp Bê Invidia</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Disappointed Noble</t>
+          <t>Quý tộc Thất Vọng</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Voidspawn: Reactor Husk</t>
+          <t>Voidspawn: Xác Thùng Phản Ứng</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Abyssal Gladius</t>
+          <t>Kiếm Vực Sâu</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Ringtail Raccoon</t>
+          <t>Gấu Mèo Đuôi Vòng</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Nhân viên Đoàn múa sư tử tốt bụng</t>
+          <t>Nhân Viên Đoàn Múa Lân Tốt Bụng</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Cluster Prism: Spectro</t>
+          <t>Lăng Kính Cụm: Spectro</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Lời mời thách đấu</t>
+          <t>Mời thách đấu</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Xem xét bản ghi nhớ</t>
+          <t>Kiểm tra tờ ghi chú</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Xieli</t>
+          <t>Tạ Lệ</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Legendary Fishing Spot</t>
+          <t>Điểm Câu Cá Huyền Thoại</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Cracked Floor</t>
+          <t>Sàn Nứt</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Nimbus Wraith</t>
+          <t>Hồn Ma Nimbus</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>: "Pulsating Heart"</t>
+          <t>: "Trái Tim Đập Thình Thịch"</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Spirited Wootter</t>
+          <t>Chim Wootter Tinh Nghịch</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Storyteller</t>
+          <t>Người Kể Chuyện</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Female Stranger</t>
+          <t>Người phụ nữ lạ mặt</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Qiqi</t>
+          <t>Tề Tề</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Chop Chop: Leftless</t>
+          <t>Chop Chop: Không Tay Trái</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Thử thách: Khu vực Suy luận II</t>
+          <t>Thử Thách: Mê Cung Suy Luận II</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Huyễn Ảnh: Sigillum</t>
+          <t>Phantom: Ấn Kết</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Lốc xoáy</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Ice Turret</t>
+          <t>Tháp Băng</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Calcharo Cube</t>
+          <t>Khối Calcharo</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tree Cage Opening</t>
+          <t>Mở Lồng Cây</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Shunan</t>
+          <t>Thuận An</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>The Binder</t>
+          <t>Kẻ Ràng Buộc</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Thử thách Nhận thức II</t>
+          <t>Thử Thách Nhận Thức II</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Ebony Gatekeeper</t>
+          <t>Người Gác Cổng Hắc Ám</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Nhân viên kích động</t>
+          <t>Nhân Viên Bồn Chồn</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>: Blazing Guardian</t>
+          <t>: Người Bảo Vệ Lửa Thiêng</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Taunt Guarding</t>
+          <t>Khiêu khích khi phòng thủ</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Người đàn ông điềm tĩnh</t>
+          <t>Người đàn ông bình tĩnh</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Người Dân Đau Buồn</t>
+          <t>Người Dân Đau Khổ</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Nhân Viên Hỗ Trợ Bất Ngờ</t>
+          <t>Thành Viên Hậu Cần Bị Sốc</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Lời Thách Đấu</t>
+          <t>Mời thách đấu</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Investigate</t>
+          <t>Điều Tra</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Distressed Senior</t>
+          <t>Bậc Trưởng Bối Đau Khổ</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Zhizhi</t>
+          <t>Chí Chí</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Wutheride Transmitter Base</t>
+          <t>Trạm Trung Chuyển Vực Gió</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Kiểm Tra Tần Số</t>
+          <t>Kiểm tra Tần số</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Snack Vendor</t>
+          <t>Người bán đồ ăn vặt</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Onlooking Kid</t>
+          <t>Đứa trẻ theo dõi</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Abby Cube</t>
+          <t>Khối Abby</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Knock</t>
+          <t>Cú Gõ</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Giao "Món Quà" Ma Quỷ Yêu Cầu</t>
+          <t>Giao "Món Quà" mà hồn ma yêu cầu đi</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Hóa Đơn</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Mighty Lightcrusher</t>
+          <t>Ánh Sáng Nghiền Nát Vĩ Đại</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Kiểm Tra Bức Tượng</t>
+          <t>Kiểm tra bức tượng</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Chỗ Ngồi Trống</t>
+          <t>Ghế trống</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Cá</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Zani Cube</t>
+          <t>Khối Zani</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Mahe's Grocery</t>
+          <t>Cửa Hàng Tạp Hóa Mahe</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Golden Fleece</t>
+          <t>Lông Cừu Vàng</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Glowing Impermanence Heron</t>
+          <t>Diệc Vô Thường Phát Quang</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Ngồi Ghế Gần Đuôi Tàu</t>
+          <t>Ngồi ghế gần đuôi tàu đi</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Hoàn Thành Nhiệm Vụ Chính Để Mở Khóa Light Builder</t>
+          <t>Hoàn thành Nhiệm Vụ Chính để mở khóa Light Builder</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Gravity Stream 10m</t>
+          <t>Dòng Trọng Lực 10m</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone Grapple</t>
+          <t>Kỹ Năng Kẹp Rùa Địa Chuông</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Curious Young Fisherman</t>
+          <t>Ngư Phủ Trẻ Tò Mò</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Sea Apple</t>
+          <t>Táo Biển</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Đến Thành Phố Honami Để Thu Thập Thêm Thông Tin</t>
+          <t>Đến Thành phố Honami để thu thập thêm thông tin</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Thùng Có Thể Phá Hủy</t>
+          <t>Thùng carton có thể phá hủy</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Fractsidus Thruster</t>
+          <t>Động Cơ Phản Lực Fractsidus</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Đọc Tờ Ghi Chú</t>
+          <t>Đọc tờ ghi chú</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Tấm Vải Bất Khuất</t>
+          <t>Vải Bất Khuất</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Giao "Món Quà" Ma Quỷ Yêu Cầu</t>
+          <t>Giao "Món Quà" mà hồn ma yêu cầu đi</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Rời Khỏi Mystery Dreamland</t>
+          <t>Rời khỏi Khu Vực Mystery Dreamland</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Tức Giận</t>
+          <t>Nhà Nghiên Cứu Giận Dữ</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Grandpa Coal</t>
+          <t>Ông Cục Than</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>"Port Business Advertisement"</t>
+          <t>"Quảng Cáo Kinh Doanh Cảng"</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Voltscourge Stalker</t>
+          <t>Kẻ Rình Rập Sét Tàn Phá</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Rương House of Wonders</t>
+          <t>Rương Ngôi Nhà Kỳ Diệu</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Rusty Spear</t>
+          <t>Giáo Gỉ</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Frail Outcast</t>
+          <t>Kẻ Lưu Đày Yếu Ớt</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Để Lại Thư Chấp Nhận Của Học Viện Startorch</t>
+          <t>Để lại thư nhập học của Học viện Startorch</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Repairer</t>
+          <t>Thợ sửa chữa</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Vào Thiên Hà Ngầm</t>
+          <t>Bước vào thiên hà ngầm</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>: Jumbled Dreams</t>
+          <t>: Những Giấc Mơ Hỗn Độn</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Basic Trophy Chest</t>
+          <t>Rương Chiến Lợi phẩm Cơ Bản</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Control Unit</t>
+          <t>Bộ Điều khiển</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Lời Thách Đấu</t>
+          <t>Mời thách đấu</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Cư Dân Hoảng Loạn</t>
+          <t>Cư dân hoảng sợ</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Qingzhao</t>
+          <t>Thanh Triệu</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Chúa tể Ngõ Đen</t>
+          <t>Chúa Tể Hẻm Đen</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Dân làng buôn chuyện</t>
+          <t>Dân Chuyện Trò</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Soaked Record</t>
+          <t>Bản ghi ướt sũng</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Energy Depletion Circle</t>
+          <t>Vòng Tròn Cạn Kiệt Năng Lượng</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Thử thách lại</t>
+          <t>Thử sức lại nào</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>White Piece</t>
+          <t>Mảnh Trắng</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Small Fishing Spot</t>
+          <t>Bãi Câu Cá Nhỏ</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Đứa trẻ cáu kỉnh</t>
+          <t>Đứa Trẻ Cáu Kỉnh</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Dương Tuyền</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Học sinh bối rối</t>
+          <t>Học Sinh Lạc Lối</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Mời bạn đồng hành cùng thưởng thức âm nhạc</t>
+          <t>Mời bạn bè cùng thưởng thức âm nhạc</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Zhuyi</t>
+          <t>Chủ Ý</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>"Ancient Calamity"</t>
+          <t>"Tai Họa Cổ Xưa"</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Zither</t>
+          <t>Đàn tranh</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Master Xuanmiao</t>
+          <t>Sư phụ Xuanmiao</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Helpful Wootter</t>
+          <t>Wootter Hữu Ích</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Communication Device</t>
+          <t>Thiết Bị Liên Lạc</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>KU-Chase</t>
+          <t>KU-Săn Đuổi</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Green Pit Lizard</t>
+          <t>Thằn Lằn Hố Xanh</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Side_Airwall_Manager_Circle_Mainstory_Exclusive</t>
+          <t>Quản Lý Vách Không Phụ_Bản Đồ Chính Truyện_Độc Quyền</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Black Piece</t>
+          <t>Mảnh Đen</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Hanolt</t>
+          <t>Ha-nốt</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Afterlife</t>
+          <t>Hậu Thế</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Pioneer Association Photographer</t>
+          <t>Nhiếp ảnh gia Hiệp hội Tiên phong</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Chàng trai trẻ</t>
+          <t>Chàng Trai Trẻ</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Hurried Passerby</t>
+          <t>Người Đi Đường Vội Vã</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Baiju</t>
+          <t>Bạch Cửu</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Nhân viên tiếp tân Jewel Boba</t>
+          <t>Nhân Viên Tiếp Tân Trà Chanh Ngọc</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Blurry Carving</t>
+          <t>Hình Khắc Mờ Ố</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Investigate</t>
+          <t>Điều Tra</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Nhận Wish Tag</t>
+          <t>Nhận Thẻ Nguyện Ước</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>The Recorder</t>
+          <t>Người Ghi Âm</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Get Preparation Credit</t>
+          <t>Nhận Tín Dụng Chuẩn Bị</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Tethys Hub</t>
+          <t>Trung Tâm Tethys</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Reminiscence: Denia</t>
+          <t>Hồi ức: Denia</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Một bia mộ lấp lánh ánh sáng mặt trăng</t>
+          <t>Ngôi mộ lấp lánh ánh trăng huyền ảo</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Điều tra cánh cổng kỳ lạ</t>
+          <t>Kiểm tra cánh cổng kỳ lạ</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Voidspawn: Kronaclaw</t>
+          <t>Voidspawn: Móng Vuốt Hắc Ám</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Luoxi</t>
+          <t>Lạc Hy</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Flip</t>
+          <t>Lật Người</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>Hạnh Phúc</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Xoay bức tượng</t>
+          <t>Xoay bức tượng.</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Huaiming</t>
+          <t>Hoài Minh</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Phantom: Lorelei</t>
+          <t>Hồn Ma: Lorelei</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Xinyi</t>
+          <t>Tân Nghi</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Sứ giả của Order</t>
+          <t>Sứ giả của Hội</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Helpful Shepherd</t>
+          <t>Người Chăn Cừu Tốt Bụng</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Ra ngoài</t>
+          <t>Ra ngoài đi</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Zhichun</t>
+          <t>Chỉ Xuân</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu Huanglong</t>
+          <t>Nhà Nghiên Cứu Huanglong</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Xinzhi</t>
+          <t>Tân Chí</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Probe</t>
+          <t>Thăm dò</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>: Mourning Thunder</t>
+          <t>: Sấm Bi Ca</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Bức ảnh của ba người</t>
+          <t>Bức Ảnh Ba Người</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Mining Drone</t>
+          <t>Drone Khai Thác</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Courier</t>
+          <t>Người đưa tin</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Bắt đầu từ nơi đã dừng lại</t>
+          <t>Bắt đầu từ nơi cậu đã dừng lại</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Panoram</t>
+          <t>Toàn cảnh</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Status Record</t>
+          <t>Lịch sử Trạng Thái</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Kumi</t>
+          <t>Kumi...</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Xunwei</t>
+          <t>Tuấn Vĩ</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Stern Courier</t>
+          <t>Người đưa tin nghiêm nghị</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Cánh cửa tầng</t>
+          <t>Cửa sàn</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Secret Bookshelf Door</t>
+          <t>Cánh Cửa Bí Mật Đằng Sau Kệ Sách</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Dreamless Dream</t>
+          <t>Giấc Mộng Vô Hồn</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Gondola Guide</t>
+          <t>Hướng dẫn viên Gondola</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Cantarella Cube</t>
+          <t>Khối Cantarella</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Nightmare: Hecate</t>
+          <t>Ác Mộng: Hecate</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Qianbu</t>
+          <t>Tiền Bố</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Pearl Leaf</t>
+          <t>Lá Ngọc Trai</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Goldenback Frog</t>
+          <t>Ếch Lưng Vàng</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Kiểm tra màn hình</t>
+          <t>Kiểm tra màn hình đi</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Người phụ nữ do dự</t>
+          <t>Người Phụ Nữ Lưỡng Lự</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Jiu</t>
+          <t>Cửu</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Nhân viên tái chế</t>
+          <t>Nhân Viên Tái Chế</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Wounded Villager</t>
+          <t>Dân Làng Bị Thương</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Đạt Cấp 3 Trung tâm Dữ liệu để mở khóa</t>
+          <t>Đạt Cấp Trung Tâm Dữ Liệu 3 để mở khóa.</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Young Dreadmane: Thunder</t>
+          <t>Dreadmane Trẻ: Sấm Sét</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Backward</t>
+          <t>Lùi lại</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>The Finale</t>
+          <t>Khúc Kết</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Công nhân thành phố</t>
+          <t>Công nhân Thành phố</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Enter "Perspective Bender"</t>
+          <t>Vào "Perspective Bender"</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Oil Painting</t>
+          <t>Bức Tranh Dầu</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Cửa vào Haven of Sprouts</t>
+          <t>Cửa Vào Mầm Xanh Thịnh Vượng</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Tacetite Twig</t>
+          <t>Cành Tổ Tacet</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Cô bé</t>
+          <t>Cô Bé</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Hoda</t>
+          <t>Hoda à...</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Track Switch</t>
+          <t>Chuyển Theo Dõi</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Hiệp sĩ hèn nhát</t>
+          <t>Hiệp Sĩ Hèn Nhát</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Tank Guardian: Light</t>
+          <t>Hộ Vệ Thiết Giáp: Quang Minh</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Xem các món ăn có sẵn</t>
+          <t>Xem các món ăn khả dụng</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Enter Parallel Perception</t>
+          <t>Vào Parallel Perception</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Felicitous Olives</t>
+          <t>Ô Liu May Mắn</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Những người trẻ đang xem</t>
+          <t>Những người trẻ đang theo dõi</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Oaknut</t>
+          <t>Hạt Sồi</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Tham gia "Thử thách Giả mạo"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Thu thập Longings</t>
+          <t>Thu thập Những Khát Khao</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone Shell</t>
+          <t>Vỏ Rùa Địa Chuông</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Nổi giận với bức tượng</t>
+          <t>Nổi Giận Trước Bức Tượng</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Mở cửa</t>
+          <t>Mở Cửa</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Đến tầng trệt</t>
+          <t>Tầng trệt</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>Lắng nghe</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Instruct "Minghu"</t>
+          <t>Hướng dẫn "Minghu"</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tượng đài bí ẩn</t>
+          <t>Bia đá bí ẩn</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Lucio Jamie</t>
+          <t>Lucio Jamie...</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Pinwen</t>
+          <t>Pinwên</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Construction Test</t>
+          <t>Bài Kiểm Tra Xây Dựng</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Uncle Li</t>
+          <t>Bác Lý</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Firecracker</t>
+          <t>Pháo Hoa</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Dingfeng</t>
+          <t>Đinh Phong</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Mourning Aix: Cannon</t>
+          <t>Aix Đau Buồn: Pháo Đài</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Tham gia "Thử thách Giả mạo"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Dig</t>
+          <t>Đào đi!</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Yingda</t>
+          <t>Doanh Đạt</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Mở kho hàng</t>
+          <t>Mở Kho Đồ</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Chờ buổi biểu diễn</t>
+          <t>Hãy chờ màn trình diễn bắt đầu.</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Tuppence</t>
+          <t>Hai xu</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>Lên tàu</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Excited Kid</t>
+          <t>Đứa trẻ phấn khích</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Levitation Group</t>
+          <t>Nhóm Bay Lơ Lửng</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Những chiếc chai trên bàn</t>
+          <t>Những chai lọ trên bàn</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>: Lightbane Reversal</t>
+          <t>: Đảo Ngược Ánh Sáng Chết</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Ei</t>
+          <t>Êi</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Về Hiệp hội Tiên phong</t>
+          <t>Về Hiệp Hội Tiên Phong</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Yibai Clinic</t>
+          <t>Phòng Khám Yibai</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Wooly Black</t>
+          <t>Wooly Đen</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Tick Tack: Havoc</t>
+          <t>Tíc Tắc: Hỗn Loạn</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Port 1 Fast Travel</t>
+          <t>Di chuyển Nhanh Cảng 1</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Uncle Bai</t>
+          <t>Chú Bạch</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Rời Trung tâm Điều hành</t>
+          <t>Rời Trung Tâm Điều Hành</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
